--- a/student_exam_analysis/student_exam_scores .xlsx
+++ b/student_exam_analysis/student_exam_scores .xlsx
@@ -2,41 +2,42 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr hidePivotFieldList="1"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AWAN\Documents\Practice Files\PROJECTS\Excel_for_data_analytics\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AWAN\Documents\Practice Files\PROJECTS\Excel_Analysis\student_exam_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <workbookProtection lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9372" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9372" firstSheet="3" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="student_exam_scores " sheetId="1" r:id="rId1"/>
-    <sheet name="Attendance and Study Hour" sheetId="4" state="hidden" r:id="rId2"/>
-    <sheet name="Previous V Exam" sheetId="8" state="hidden" r:id="rId3"/>
-    <sheet name="Improvement and Attendance" sheetId="18" state="hidden" r:id="rId4"/>
-    <sheet name="Improvement " sheetId="19" state="hidden" r:id="rId5"/>
+    <sheet name="Attendance and Study Hour" sheetId="4" r:id="rId2"/>
+    <sheet name="Previous V Exam" sheetId="8" r:id="rId3"/>
+    <sheet name="Improvement and Attendance" sheetId="18" r:id="rId4"/>
+    <sheet name="Improvement " sheetId="19" r:id="rId5"/>
     <sheet name="Previous and Study Hour" sheetId="11" state="hidden" r:id="rId6"/>
     <sheet name="Exam and study Hour" sheetId="12" state="hidden" r:id="rId7"/>
     <sheet name="Dash Board" sheetId="17" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'student_exam_scores '!$A$1:$F$202</definedName>
+    <definedName name="Slicer_Attendance">#N/A</definedName>
     <definedName name="Slicer_Attendance_Percent">#N/A</definedName>
     <definedName name="Slicer_Hours_Studied">#N/A</definedName>
   </definedNames>
   <calcPr calcId="152511" calcMode="manual"/>
   <pivotCaches>
-    <pivotCache cacheId="25" r:id="rId9"/>
-    <pivotCache cacheId="26" r:id="rId10"/>
+    <pivotCache cacheId="2" r:id="rId9"/>
+    <pivotCache cacheId="3" r:id="rId10"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
         <x14:slicerCache r:id="rId11"/>
         <x14:slicerCache r:id="rId12"/>
+        <x14:slicerCache r:id="rId13"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="256">
   <si>
     <t>S001</t>
   </si>
@@ -755,12 +756,6 @@
   </si>
   <si>
     <t>90.3-100.3</t>
-  </si>
-  <si>
-    <t>11-13</t>
-  </si>
-  <si>
-    <t>12-14</t>
   </si>
   <si>
     <t>SCORE</t>
@@ -1940,6 +1935,37 @@
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:pivotFmts>
       <c:pivotFmt>
@@ -2087,10 +2113,10 @@
                   <c:v>80.3-90.3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>60.3-70.3</c:v>
+                  <c:v>50.3-60.3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50.3-60.3</c:v>
+                  <c:v>60.3-70.3</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>70.3-80.3</c:v>
@@ -2108,13 +2134,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>20.799999999999997</c:v>
+                  <c:v>20.8</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.1000000000000014</c:v>
+                  <c:v>11.700000000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11.700000000000001</c:v>
+                  <c:v>8.1000000000000014</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>12.1</c:v>
@@ -2159,10 +2185,10 @@
                   <c:v>80.3-90.3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>60.3-70.3</c:v>
+                  <c:v>50.3-60.3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50.3-60.3</c:v>
+                  <c:v>60.3-70.3</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>70.3-80.3</c:v>
@@ -2180,13 +2206,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>36.800000000000004</c:v>
+                  <c:v>36.799999999999997</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>45.400000000000006</c:v>
+                  <c:v>41.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>41.5</c:v>
+                  <c:v>45.400000000000006</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>25.8</c:v>
@@ -2231,10 +2257,10 @@
                   <c:v>80.3-90.3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>60.3-70.3</c:v>
+                  <c:v>50.3-60.3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50.3-60.3</c:v>
+                  <c:v>60.3-70.3</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>70.3-80.3</c:v>
@@ -2255,10 +2281,10 @@
                   <c:v>68.599999999999994</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>23.700000000000003</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>37</c:v>
+                  <c:v>23.7</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>34.300000000000004</c:v>
@@ -2303,10 +2329,10 @@
                   <c:v>80.3-90.3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>60.3-70.3</c:v>
+                  <c:v>50.3-60.3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50.3-60.3</c:v>
+                  <c:v>60.3-70.3</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>70.3-80.3</c:v>
@@ -2327,10 +2353,10 @@
                   <c:v>63.500000000000007</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>70.600000000000009</c:v>
+                  <c:v>55.2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>55.2</c:v>
+                  <c:v>70.600000000000009</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>31</c:v>
@@ -2375,10 +2401,10 @@
                   <c:v>80.3-90.3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>60.3-70.3</c:v>
+                  <c:v>50.3-60.3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50.3-60.3</c:v>
+                  <c:v>60.3-70.3</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>70.3-80.3</c:v>
@@ -2399,88 +2425,16 @@
                   <c:v>58.699999999999996</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>48.6</c:v>
+                  <c:v>72.100000000000009</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>72.100000000000009</c:v>
+                  <c:v>48.6</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>90.2</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>70.7</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:ser>
-          <c:idx val="5"/>
-          <c:order val="5"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Attendance and Study Hour'!$G$3:$G$4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>11-13</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent6"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Attendance and Study Hour'!$A$5:$A$10</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>80.3-90.3</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>60.3-70.3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>50.3-60.3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>70.3-80.3</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>90.3-100.3</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Attendance and Study Hour'!$G$5:$G$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>45.400000000000006</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>57.199999999999996</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>35.1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>57.7</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>23.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2496,11 +2450,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="427455072"/>
-        <c:axId val="427456248"/>
+        <c:axId val="298596032"/>
+        <c:axId val="298595640"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="427455072"/>
+        <c:axId val="298596032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2543,7 +2497,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="427456248"/>
+        <c:crossAx val="298595640"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2551,7 +2505,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="427456248"/>
+        <c:axId val="298595640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2588,7 +2542,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="427455072"/>
+        <c:crossAx val="298596032"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2602,6 +2556,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3882,25 +3837,22 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Exam and study Hour'!$A$4:$A$10</c:f>
+              <c:f>'Exam and study Hour'!$A$4:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>12-14</c:v>
+                  <c:v>10-12</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10-12</c:v>
+                  <c:v>8-10</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8-10</c:v>
+                  <c:v>6-8</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6-8</c:v>
+                  <c:v>4-6</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4-6</c:v>
-                </c:pt>
-                <c:pt idx="5">
                   <c:v>2-4</c:v>
                 </c:pt>
               </c:strCache>
@@ -3908,26 +3860,23 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Exam and study Hour'!$B$4:$B$10</c:f>
+              <c:f>'Exam and study Hour'!$B$4:$B$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>43.136842105263156</c:v>
+                  <c:v>40.1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>40.1</c:v>
+                  <c:v>35.761764705882349</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>35.761764705882349</c:v>
+                  <c:v>33.529411764705884</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>33.529411764705884</c:v>
+                  <c:v>29.211111111111105</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>29.211111111111116</c:v>
-                </c:pt>
-                <c:pt idx="5">
                   <c:v>27.576470588235303</c:v>
                 </c:pt>
               </c:numCache>
@@ -3944,11 +3893,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="427443704"/>
-        <c:axId val="427445272"/>
+        <c:axId val="377727320"/>
+        <c:axId val="377723400"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="427443704"/>
+        <c:axId val="377727320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3988,7 +3937,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="427445272"/>
+        <c:crossAx val="377723400"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3996,7 +3945,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="427445272"/>
+        <c:axId val="377723400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4030,7 +3979,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="427443704"/>
+        <c:crossAx val="377727320"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4392,25 +4341,22 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Previous V Exam'!$A$5:$A$11</c:f>
+              <c:f>'Previous V Exam'!$A$5:$A$10</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>11-13</c:v>
+                  <c:v>9-11</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9-11</c:v>
+                  <c:v>7-9</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7-9</c:v>
+                  <c:v>5-7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5-7</c:v>
+                  <c:v>3-5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3-5</c:v>
-                </c:pt>
-                <c:pt idx="5">
                   <c:v>1-3</c:v>
                 </c:pt>
               </c:strCache>
@@ -4418,26 +4364,23 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Previous V Exam'!$B$5:$B$11</c:f>
+              <c:f>'Previous V Exam'!$B$5:$B$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>66.315789473684205</c:v>
+                  <c:v>70.352941176470594</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>70.352941176470594</c:v>
+                  <c:v>67.17647058823529</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>67.17647058823529</c:v>
+                  <c:v>66.147058823529406</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>66.147058823529406</c:v>
+                  <c:v>63.422222222222224</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>63.422222222222224</c:v>
-                </c:pt>
-                <c:pt idx="5">
                   <c:v>68.264705882352942</c:v>
                 </c:pt>
               </c:numCache>
@@ -4470,25 +4413,22 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Previous V Exam'!$A$5:$A$11</c:f>
+              <c:f>'Previous V Exam'!$A$5:$A$10</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>11-13</c:v>
+                  <c:v>9-11</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9-11</c:v>
+                  <c:v>7-9</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7-9</c:v>
+                  <c:v>5-7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5-7</c:v>
+                  <c:v>3-5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3-5</c:v>
-                </c:pt>
-                <c:pt idx="5">
                   <c:v>1-3</c:v>
                 </c:pt>
               </c:strCache>
@@ -4496,26 +4436,23 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Previous V Exam'!$C$5:$C$11</c:f>
+              <c:f>'Previous V Exam'!$C$5:$C$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>43.136842105263156</c:v>
+                  <c:v>40.1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>40.1</c:v>
+                  <c:v>35.761764705882349</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>35.761764705882349</c:v>
+                  <c:v>33.529411764705884</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>33.529411764705884</c:v>
+                  <c:v>29.211111111111105</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>29.211111111111116</c:v>
-                </c:pt>
-                <c:pt idx="5">
                   <c:v>27.576470588235303</c:v>
                 </c:pt>
               </c:numCache>
@@ -4532,11 +4469,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="427446840"/>
-        <c:axId val="427447624"/>
+        <c:axId val="377723792"/>
+        <c:axId val="377728104"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="427446840"/>
+        <c:axId val="377723792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4576,7 +4513,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="427447624"/>
+        <c:crossAx val="377728104"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4584,7 +4521,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="427447624"/>
+        <c:axId val="377728104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4618,7 +4555,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="427446840"/>
+        <c:crossAx val="377723792"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4700,571 +4637,6 @@
 </file>
 
 <file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr marL="0" marR="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-              <a:lnSpc>
-                <a:spcPct val="100000"/>
-              </a:lnSpc>
-              <a:spcBef>
-                <a:spcPts val="0"/>
-              </a:spcBef>
-              <a:spcAft>
-                <a:spcPts val="0"/>
-              </a:spcAft>
-              <a:buClrTx/>
-              <a:buSzTx/>
-              <a:buFontTx/>
-              <a:buNone/>
-              <a:tabLst/>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0" i="0" baseline="0">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-                <a:effectLst/>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:rPr>
-              <a:t>Does attendance affect student grade? </a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US" sz="1400">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:endParaRPr>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.17226377952755909"/>
-          <c:y val="4.6296296296296294E-3"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr marL="0" marR="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.11393400824896888"/>
-          <c:y val="0.17275362318840579"/>
-          <c:w val="0.83219310730448548"/>
-          <c:h val="0.5539783179276504"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:barChart>
-        <c:barDir val="bar"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Improvement '!$C$2</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Decline</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Improvement '!$B$3:$B$7</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>91-100</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>71-80</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>61-70</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>50-60</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>81-90</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Improvement '!$C$3:$C$7</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>37</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>38</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>44</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>49</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Improvement '!$D$2</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Improved</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Improvement '!$B$3:$B$7</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>91-100</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>71-80</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>61-70</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>50-60</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>81-90</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Improvement '!$D$3:$D$7</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:dLbls>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="182"/>
-        <c:axId val="631488488"/>
-        <c:axId val="631479472"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="631488488"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="631479472"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="631479472"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="low"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-120000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="0"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="631488488"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.34326984126984122"/>
-          <c:y val="0.90217322834645663"/>
-          <c:w val="0.31346006749156358"/>
-          <c:h val="9.782677165354331E-2"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:noFill/>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:noFill/>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -5563,7 +4935,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -5876,6 +5248,415 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1200" b="0" i="0" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>Does attendance affect student grade? </a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" sz="1200">
+              <a:effectLst/>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.20115966754155734"/>
+          <c:y val="3.7037037037037035E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Improvement '!$C$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Decline</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Improvement '!$B$3:$B$7</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>91-100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>71-80</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>61-70</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>50-60</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>81-90</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Improvement '!$C$3:$C$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>49</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Improvement '!$D$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Improved</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Improvement '!$B$3:$B$7</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>91-100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>71-80</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>61-70</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>50-60</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>81-90</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Improvement '!$D$3:$D$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="386335832"/>
+        <c:axId val="386334264"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="386335832"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="386334264"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="386334264"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="50"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="386335832"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
@@ -5969,25 +5750,22 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Previous V Exam'!$A$5:$A$11</c:f>
+              <c:f>'Previous V Exam'!$A$5:$A$10</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>11-13</c:v>
+                  <c:v>9-11</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9-11</c:v>
+                  <c:v>7-9</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7-9</c:v>
+                  <c:v>5-7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5-7</c:v>
+                  <c:v>3-5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3-5</c:v>
-                </c:pt>
-                <c:pt idx="5">
                   <c:v>1-3</c:v>
                 </c:pt>
               </c:strCache>
@@ -5995,26 +5773,23 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Previous V Exam'!$B$5:$B$11</c:f>
+              <c:f>'Previous V Exam'!$B$5:$B$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>66.315789473684205</c:v>
+                  <c:v>70.352941176470594</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>70.352941176470594</c:v>
+                  <c:v>67.17647058823529</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>67.17647058823529</c:v>
+                  <c:v>66.147058823529406</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>66.147058823529406</c:v>
+                  <c:v>63.422222222222224</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>63.422222222222224</c:v>
-                </c:pt>
-                <c:pt idx="5">
                   <c:v>68.264705882352942</c:v>
                 </c:pt>
               </c:numCache>
@@ -6047,25 +5822,22 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Previous V Exam'!$A$5:$A$11</c:f>
+              <c:f>'Previous V Exam'!$A$5:$A$10</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>11-13</c:v>
+                  <c:v>9-11</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9-11</c:v>
+                  <c:v>7-9</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7-9</c:v>
+                  <c:v>5-7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5-7</c:v>
+                  <c:v>3-5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3-5</c:v>
-                </c:pt>
-                <c:pt idx="5">
                   <c:v>1-3</c:v>
                 </c:pt>
               </c:strCache>
@@ -6073,26 +5845,23 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Previous V Exam'!$C$5:$C$11</c:f>
+              <c:f>'Previous V Exam'!$C$5:$C$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>43.136842105263156</c:v>
+                  <c:v>40.1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>40.1</c:v>
+                  <c:v>35.761764705882349</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>35.761764705882349</c:v>
+                  <c:v>33.529411764705884</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>33.529411764705884</c:v>
+                  <c:v>29.211111111111105</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>29.211111111111116</c:v>
-                </c:pt>
-                <c:pt idx="5">
                   <c:v>27.576470588235303</c:v>
                 </c:pt>
               </c:numCache>
@@ -6109,11 +5878,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="427457032"/>
-        <c:axId val="427452328"/>
+        <c:axId val="298594464"/>
+        <c:axId val="298591328"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="427457032"/>
+        <c:axId val="298594464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6156,7 +5925,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="427452328"/>
+        <c:crossAx val="298591328"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6164,7 +5933,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="427452328"/>
+        <c:axId val="298591328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6201,7 +5970,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="427457032"/>
+        <c:crossAx val="298594464"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6539,11 +6308,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="182"/>
-        <c:axId val="427446448"/>
-        <c:axId val="427450368"/>
+        <c:axId val="298593680"/>
+        <c:axId val="298589368"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="427446448"/>
+        <c:axId val="298593680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6586,7 +6355,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="427450368"/>
+        <c:crossAx val="298589368"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6594,7 +6363,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="427450368"/>
+        <c:axId val="298589368"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6631,7 +6400,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="427446448"/>
+        <c:crossAx val="298593680"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6723,572 +6492,6 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr marL="0" marR="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-              <a:lnSpc>
-                <a:spcPct val="100000"/>
-              </a:lnSpc>
-              <a:spcBef>
-                <a:spcPts val="0"/>
-              </a:spcBef>
-              <a:spcAft>
-                <a:spcPts val="0"/>
-              </a:spcAft>
-              <a:buClrTx/>
-              <a:buSzTx/>
-              <a:buFontTx/>
-              <a:buNone/>
-              <a:tabLst/>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:sysClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1200" b="0" i="0" baseline="0">
-                <a:effectLst/>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:rPr>
-              <a:t>Does attendance affect student grade? </a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US" sz="1200">
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:endParaRPr>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.17226377952755909"/>
-          <c:y val="4.6296296296296294E-3"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr marL="0" marR="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:sysClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="bar"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Improvement '!$C$2</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Decline</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Improvement '!$B$3:$B$7</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>91-100</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>71-80</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>61-70</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>50-60</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>81-90</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Improvement '!$C$3:$C$7</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>37</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>38</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>44</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>49</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Improvement '!$D$2</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Improved</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Improvement '!$B$3:$B$7</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>91-100</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>71-80</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>61-70</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>50-60</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>81-90</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Improvement '!$D$3:$D$7</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:dLbls>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="182"/>
-        <c:axId val="427450760"/>
-        <c:axId val="427449584"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="427450760"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="427449584"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="427449584"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="427450760"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:layout/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -7627,7 +6830,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -7824,9 +7027,7 @@
               </c:spPr>
             </c:leaderLines>
             <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-              </c:ext>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
             </c:extLst>
           </c:dLbls>
           <c:cat>
@@ -7870,6 +7071,422 @@
         </c:dLbls>
         <c:firstSliceAng val="0"/>
       </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1200" b="0" i="0" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>Does attendance affect student grade? </a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" sz="1200">
+              <a:effectLst/>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.20115966754155734"/>
+          <c:y val="3.7037037037037035E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Improvement '!$C$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Decline</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Improvement '!$B$3:$B$7</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>91-100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>71-80</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>61-70</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>50-60</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>81-90</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Improvement '!$C$3:$C$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>49</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Improvement '!$D$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Improved</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Improvement '!$B$3:$B$7</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>91-100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>71-80</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>61-70</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>50-60</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>81-90</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Improvement '!$D$3:$D$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="386346808"/>
+        <c:axId val="386347200"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="386346808"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="386347200"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="386347200"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="50"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="386346808"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -9050,9 +8667,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Previous and Study Hour'!$A$4:$A$10</c:f>
+              <c:f>'Previous and Study Hour'!$A$4:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>9-11</c:v>
                 </c:pt>
@@ -9063,12 +8680,9 @@
                   <c:v>7-9</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11-13</c:v>
+                  <c:v>5-7</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5-7</c:v>
-                </c:pt>
-                <c:pt idx="5">
                   <c:v>3-5</c:v>
                 </c:pt>
               </c:strCache>
@@ -9076,10 +8690,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Previous and Study Hour'!$B$4:$B$10</c:f>
+              <c:f>'Previous and Study Hour'!$B$4:$B$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>70.352941176470594</c:v>
                 </c:pt>
@@ -9090,12 +8704,9 @@
                   <c:v>67.17647058823529</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>66.315789473684205</c:v>
+                  <c:v>66.147058823529406</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>66.147058823529406</c:v>
-                </c:pt>
-                <c:pt idx="5">
                   <c:v>63.422222222222224</c:v>
                 </c:pt>
               </c:numCache>
@@ -9112,11 +8723,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="427444880"/>
-        <c:axId val="427451544"/>
+        <c:axId val="377726536"/>
+        <c:axId val="377724968"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="427444880"/>
+        <c:axId val="377726536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9159,7 +8770,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="427451544"/>
+        <c:crossAx val="377724968"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9167,7 +8778,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="427451544"/>
+        <c:axId val="377724968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9204,7 +8815,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="427444880"/>
+        <c:crossAx val="377726536"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10427,25 +10038,22 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Exam and study Hour'!$A$4:$A$10</c:f>
+              <c:f>'Exam and study Hour'!$A$4:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>12-14</c:v>
+                  <c:v>10-12</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10-12</c:v>
+                  <c:v>8-10</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8-10</c:v>
+                  <c:v>6-8</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6-8</c:v>
+                  <c:v>4-6</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4-6</c:v>
-                </c:pt>
-                <c:pt idx="5">
                   <c:v>2-4</c:v>
                 </c:pt>
               </c:strCache>
@@ -10453,26 +10061,23 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Exam and study Hour'!$B$4:$B$10</c:f>
+              <c:f>'Exam and study Hour'!$B$4:$B$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>43.136842105263156</c:v>
+                  <c:v>40.1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>40.1</c:v>
+                  <c:v>35.761764705882349</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>35.761764705882349</c:v>
+                  <c:v>33.529411764705884</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>33.529411764705884</c:v>
+                  <c:v>29.211111111111105</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>29.211111111111116</c:v>
-                </c:pt>
-                <c:pt idx="5">
                   <c:v>27.576470588235303</c:v>
                 </c:pt>
               </c:numCache>
@@ -10489,11 +10094,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="427441744"/>
-        <c:axId val="427451936"/>
+        <c:axId val="377724576"/>
+        <c:axId val="377727712"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="427441744"/>
+        <c:axId val="377724576"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10536,7 +10141,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="427451936"/>
+        <c:crossAx val="377727712"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10544,7 +10149,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="427451936"/>
+        <c:axId val="377727712"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10581,7 +10186,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="427441744"/>
+        <c:crossAx val="377724576"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11112,10 +10717,10 @@
                   <c:v>80.3-90.3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>60.3-70.3</c:v>
+                  <c:v>50.3-60.3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50.3-60.3</c:v>
+                  <c:v>60.3-70.3</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>70.3-80.3</c:v>
@@ -11133,13 +10738,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>20.799999999999997</c:v>
+                  <c:v>20.8</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.1000000000000014</c:v>
+                  <c:v>11.700000000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11.700000000000001</c:v>
+                  <c:v>8.1000000000000014</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>12.1</c:v>
@@ -11184,10 +10789,10 @@
                   <c:v>80.3-90.3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>60.3-70.3</c:v>
+                  <c:v>50.3-60.3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50.3-60.3</c:v>
+                  <c:v>60.3-70.3</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>70.3-80.3</c:v>
@@ -11205,13 +10810,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>36.800000000000004</c:v>
+                  <c:v>36.799999999999997</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>45.400000000000006</c:v>
+                  <c:v>41.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>41.5</c:v>
+                  <c:v>45.400000000000006</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>25.8</c:v>
@@ -11256,10 +10861,10 @@
                   <c:v>80.3-90.3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>60.3-70.3</c:v>
+                  <c:v>50.3-60.3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50.3-60.3</c:v>
+                  <c:v>60.3-70.3</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>70.3-80.3</c:v>
@@ -11280,10 +10885,10 @@
                   <c:v>68.599999999999994</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>23.700000000000003</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>37</c:v>
+                  <c:v>23.7</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>34.300000000000004</c:v>
@@ -11328,10 +10933,10 @@
                   <c:v>80.3-90.3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>60.3-70.3</c:v>
+                  <c:v>50.3-60.3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50.3-60.3</c:v>
+                  <c:v>60.3-70.3</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>70.3-80.3</c:v>
@@ -11352,10 +10957,10 @@
                   <c:v>63.500000000000007</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>70.600000000000009</c:v>
+                  <c:v>55.2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>55.2</c:v>
+                  <c:v>70.600000000000009</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>31</c:v>
@@ -11400,10 +11005,10 @@
                   <c:v>80.3-90.3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>60.3-70.3</c:v>
+                  <c:v>50.3-60.3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50.3-60.3</c:v>
+                  <c:v>60.3-70.3</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>70.3-80.3</c:v>
@@ -11424,88 +11029,16 @@
                   <c:v>58.699999999999996</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>48.6</c:v>
+                  <c:v>72.100000000000009</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>72.100000000000009</c:v>
+                  <c:v>48.6</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>90.2</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>70.7</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:ser>
-          <c:idx val="5"/>
-          <c:order val="5"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Attendance and Study Hour'!$G$3:$G$4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>11-13</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent6"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Attendance and Study Hour'!$A$5:$A$10</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>80.3-90.3</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>60.3-70.3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>50.3-60.3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>70.3-80.3</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>90.3-100.3</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Attendance and Study Hour'!$G$5:$G$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>45.400000000000006</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>57.199999999999996</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>35.1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>57.7</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>23.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11521,11 +11054,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="427442528"/>
-        <c:axId val="427442920"/>
+        <c:axId val="377722224"/>
+        <c:axId val="377725360"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="427442528"/>
+        <c:axId val="377722224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11565,7 +11098,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="427442920"/>
+        <c:crossAx val="377725360"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11573,7 +11106,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="427442920"/>
+        <c:axId val="377725360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11607,7 +11140,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="427442528"/>
+        <c:crossAx val="377722224"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11809,13 +11342,10 @@
 </file>
 
 <file path=xl/charts/colors12.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="11">
   <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
   <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
   <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
   <cs:variation/>
   <cs:variation>
     <a:lumMod val="60000"/>
@@ -11849,10 +11379,13 @@
 </file>
 
 <file path=xl/charts/colors13.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="11">
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
   <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
   <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
   <cs:variation/>
   <cs:variation>
     <a:lumMod val="60000"/>
@@ -13755,7 +13288,7 @@
 </file>
 
 <file path=xl/charts/style12.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -13812,7 +13345,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -13863,6 +13396,13 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -13873,12 +13413,19 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -13916,7 +13463,7 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -14779,7 +14326,7 @@
 </file>
 
 <file path=xl/charts/style14.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -14836,7 +14383,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -14887,13 +14434,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -14904,19 +14444,12 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="25400">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -14954,7 +14487,7 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -16306,7 +15839,7 @@
 </file>
 
 <file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -16363,7 +15896,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -16414,6 +15947,13 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -16424,12 +15964,19 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -16467,7 +16014,7 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -17330,7 +16877,7 @@
 </file>
 
 <file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -17387,7 +16934,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -17438,13 +16985,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -17455,19 +16995,12 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="25400">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -17505,7 +17038,7 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -19397,8 +18930,8 @@
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
@@ -19603,6 +19136,78 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>129540</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>129540</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>165735</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="3" name="Attendance"/>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Attendance"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="8496300" y="1722120"/>
+              <a:ext cx="1828800" cy="2466975"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -19610,20 +19215,20 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>106680</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>83820</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>426720</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>640080</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>68580</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>160020</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvPr id="7" name="Chart 6"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -19640,20 +19245,20 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>662940</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>274320</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>259080</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>137160</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="7" name="Chart 6"/>
+        <xdr:cNvPr id="4" name="Chart 3"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -19670,20 +19275,20 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>525780</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>449580</xdr:colOff>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>167640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>220980</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>167640</xdr:rowOff>
+      <xdr:colOff>137160</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3"/>
+        <xdr:cNvPr id="5" name="Chart 4"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -20203,12 +19808,12 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>132927</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>115993</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="11917680" cy="1249258"/>
+    <xdr:ext cx="6286500" cy="1249258"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="TextBox 1"/>
@@ -20216,8 +19821,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="746760" y="137160"/>
-          <a:ext cx="11917680" cy="1249258"/>
+          <a:off x="3545417" y="295910"/>
+          <a:ext cx="6286500" cy="1249258"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -20655,8 +20260,8 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="7" name="Hours_Studied 3"/>
@@ -20673,7 +20278,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -20759,8 +20364,8 @@
       <xdr:row>40</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="12" name="Attendance_Percent 1"/>
@@ -20777,7 +20382,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -20852,38 +20457,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>328084</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>42334</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>31751</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>116419</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="20" name="Chart 19"/>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>63501</xdr:colOff>
       <xdr:row>10</xdr:row>
@@ -20908,7 +20481,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -20930,6 +20503,38 @@
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="50" name="Chart 49"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>328084</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>84666</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>550334</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>86783</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="28" name="Chart 27"/>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -20971,7 +20576,7 @@
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
+      <x14:pivotCacheDefinition pivotCacheId="2"/>
     </ext>
   </extLst>
 </pivotCacheDefinition>
@@ -23036,20 +22641,20 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
-  <location ref="L2:S9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable6" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
+  <location ref="A3:G10" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField showAll="0"/>
     <pivotField axis="axisCol" dataField="1" numFmtId="164" showAll="0">
       <items count="9">
-        <item x="0"/>
+        <item h="1" x="0"/>
         <item x="1"/>
         <item x="2"/>
         <item x="3"/>
         <item x="4"/>
         <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
+        <item h="1" x="6"/>
+        <item h="1" x="7"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -23086,10 +22691,10 @@
       <x v="1"/>
     </i>
     <i>
-      <x v="3"/>
+      <x v="4"/>
     </i>
     <i>
-      <x v="4"/>
+      <x v="3"/>
     </i>
     <i>
       <x v="2"/>
@@ -23104,7 +22709,7 @@
   <colFields count="1">
     <field x="1"/>
   </colFields>
-  <colItems count="7">
+  <colItems count="6">
     <i>
       <x v="1"/>
     </i>
@@ -23120,15 +22725,12 @@
     <i>
       <x v="5"/>
     </i>
-    <i>
-      <x v="6"/>
-    </i>
     <i t="grand">
       <x/>
     </i>
   </colItems>
   <dataFields count="1">
-    <dataField name="Count of Hours_Studied" fld="1" subtotal="count" baseField="3" baseItem="1"/>
+    <dataField name="Sum of Hours_Studied" fld="1" baseField="3" baseItem="4"/>
   </dataFields>
   <formats count="4">
     <format dxfId="15">
@@ -23318,20 +22920,20 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable6" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
-  <location ref="A3:H10" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
+  <location ref="L2:R9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField showAll="0"/>
     <pivotField axis="axisCol" dataField="1" numFmtId="164" showAll="0">
       <items count="9">
-        <item x="0"/>
+        <item h="1" x="0"/>
         <item x="1"/>
         <item x="2"/>
         <item x="3"/>
         <item x="4"/>
         <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
+        <item h="1" x="6"/>
+        <item h="1" x="7"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -23368,16 +22970,16 @@
       <x v="1"/>
     </i>
     <i>
+      <x v="4"/>
+    </i>
+    <i>
       <x v="3"/>
     </i>
     <i>
-      <x v="4"/>
+      <x/>
     </i>
     <i>
       <x v="2"/>
-    </i>
-    <i>
-      <x/>
     </i>
     <i t="grand">
       <x/>
@@ -23386,7 +22988,7 @@
   <colFields count="1">
     <field x="1"/>
   </colFields>
-  <colItems count="7">
+  <colItems count="6">
     <i>
       <x v="1"/>
     </i>
@@ -23402,15 +23004,12 @@
     <i>
       <x v="5"/>
     </i>
-    <i>
-      <x v="6"/>
-    </i>
     <i t="grand">
       <x/>
     </i>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of Hours_Studied" fld="1" baseField="3" baseItem="4"/>
+    <dataField name="Count of Hours_Studied" fld="1" subtotal="count" baseField="3" baseItem="1"/>
   </dataFields>
   <formats count="4">
     <format dxfId="19">
@@ -23600,8 +23199,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable6" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="26">
-  <location ref="A4:C11" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable6" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="27">
+  <location ref="A4:C10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField showAll="0" measureFilter="1" sortType="descending">
       <autoSortScope>
@@ -23616,14 +23215,14 @@
     </pivotField>
     <pivotField axis="axisRow" numFmtId="164" showAll="0" sortType="descending">
       <items count="9">
-        <item x="0"/>
+        <item h="1" x="0"/>
         <item x="1"/>
         <item x="2"/>
         <item x="3"/>
         <item x="4"/>
         <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
+        <item h="1" x="6"/>
+        <item h="1" x="7"/>
         <item t="default"/>
       </items>
       <autoSortScope>
@@ -23664,10 +23263,7 @@
   <rowFields count="1">
     <field x="1"/>
   </rowFields>
-  <rowItems count="7">
-    <i>
-      <x v="6"/>
-    </i>
+  <rowItems count="6">
     <i>
       <x v="5"/>
     </i>
@@ -24097,7 +23693,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable4" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="40">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="40">
   <location ref="A3:C7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0" sortType="ascending">
@@ -24200,20 +23796,20 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable6" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
-  <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable6" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
+  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" numFmtId="164" showAll="0" sortType="descending">
       <items count="9">
-        <item x="0"/>
+        <item h="1" x="0"/>
         <item x="1"/>
         <item x="2"/>
         <item x="3"/>
         <item x="4"/>
         <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
+        <item h="1" x="6"/>
+        <item h="1" x="7"/>
         <item t="default"/>
       </items>
       <autoSortScope>
@@ -24245,7 +23841,7 @@
   <rowFields count="1">
     <field x="1"/>
   </rowFields>
-  <rowItems count="7">
+  <rowItems count="6">
     <i>
       <x v="5"/>
     </i>
@@ -24254,9 +23850,6 @@
     </i>
     <i>
       <x v="4"/>
-    </i>
-    <i>
-      <x v="6"/>
     </i>
     <i>
       <x v="3"/>
@@ -24309,20 +23902,20 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable6" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
-  <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable6" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
+  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField showAll="0"/>
     <pivotField numFmtId="164" showAll="0">
       <items count="9">
-        <item x="0"/>
+        <item h="1" x="0"/>
         <item x="1"/>
         <item x="2"/>
         <item x="3"/>
         <item x="4"/>
         <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
+        <item h="1" x="6"/>
+        <item h="1" x="7"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -24366,10 +23959,7 @@
   <rowFields count="1">
     <field x="2"/>
   </rowFields>
-  <rowItems count="7">
-    <i>
-      <x v="6"/>
-    </i>
+  <rowItems count="6">
     <i>
       <x v="5"/>
     </i>
@@ -24475,14 +24065,31 @@
   <data>
     <tabular pivotCacheId="1">
       <items count="8">
-        <i x="6" s="1"/>
+        <i x="6"/>
         <i x="1" s="1"/>
         <i x="2" s="1"/>
         <i x="3" s="1"/>
         <i x="4" s="1"/>
         <i x="5" s="1"/>
-        <i x="0" s="1" nd="1"/>
-        <i x="7" s="1" nd="1"/>
+        <i x="0" nd="1"/>
+        <i x="7" nd="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache3.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x" name="Slicer_Attendance" sourceName="Attendance">
+  <pivotTables>
+    <pivotTable tabId="18" name="PivotTable4"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="2">
+      <items count="3">
+        <i x="2" s="1"/>
+        <i x="0" s="1"/>
+        <i x="1" s="1"/>
       </items>
     </tabular>
   </data>
@@ -24502,6 +24109,12 @@
 </file>
 
 <file path=xl/slicers/slicer3.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <slicer name="Attendance" cache="Slicer_Attendance" caption="Attendance" rowHeight="234950"/>
+</slicers>
+</file>
+
+<file path=xl/slicers/slicer4.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <slicer name="Attendance_Percent 1" cache="Slicer_Attendance_Percent" caption="Attendance_Percent" showCaption="0" style="SlicerStyleDark3" rowHeight="234950"/>
   <slicer name="Hours_Studied 3" cache="Slicer_Hours_Studied" caption="Hours_Studied" startItem="1" showCaption="0" style="SlicerStyleDark3" rowHeight="234950"/>
@@ -24813,7 +24426,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R203"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" customWidth="1"/>
     <col min="2" max="2" width="13.88671875" style="2" customWidth="1"/>
@@ -24832,7 +24445,7 @@
     <col min="17" max="17" width="8.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>200</v>
       </c>
@@ -24840,7 +24453,7 @@
         <v>201</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>202</v>
@@ -24852,29 +24465,29 @@
         <v>204</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>227</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="R1" s="18"/>
     </row>
-    <row r="2" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -24923,7 +24536,7 @@
       </c>
       <c r="R2" s="4"/>
     </row>
-    <row r="3" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -24972,7 +24585,7 @@
       </c>
       <c r="R3" s="4"/>
     </row>
-    <row r="4" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -25021,7 +24634,7 @@
       </c>
       <c r="R4" s="4"/>
     </row>
-    <row r="5" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -25070,7 +24683,7 @@
       </c>
       <c r="R5" s="4"/>
     </row>
-    <row r="6" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -25127,7 +24740,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -25175,7 +24788,7 @@
         <v>Increase</v>
       </c>
       <c r="O7" s="14" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="P7">
         <f>COUNTIF($I$2:$I$201,O7)</f>
@@ -25185,7 +24798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -25233,7 +24846,7 @@
         <v>Increase</v>
       </c>
       <c r="O8" s="14" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="P8">
         <f>COUNTIF($I$2:$I$202,O8)</f>
@@ -25243,7 +24856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -25291,7 +24904,7 @@
         <v>Increase</v>
       </c>
       <c r="O9" s="14" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="P9">
         <f>COUNTIF($I$2:$I$203,O9)</f>
@@ -25301,7 +24914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -25349,7 +24962,7 @@
         <v>Increase</v>
       </c>
       <c r="O10" s="14" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="P10">
         <f>COUNTIF($I$2:$I$204,O10)</f>
@@ -25359,7 +24972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>183</v>
       </c>
@@ -25407,7 +25020,7 @@
         <v>Increase</v>
       </c>
       <c r="O11" s="14" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="P11">
         <f>COUNTIF($I$2:$I$205,O11)</f>
@@ -25417,7 +25030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>70</v>
       </c>
@@ -25465,7 +25078,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -25513,16 +25126,16 @@
         <v>Increase</v>
       </c>
       <c r="O13" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="P13" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q13" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="P13" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="Q13" s="14" t="s">
-        <v>240</v>
-      </c>
     </row>
-    <row r="14" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>124</v>
       </c>
@@ -25570,7 +25183,7 @@
         <v>Increase</v>
       </c>
       <c r="O14" s="17" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="P14" s="16">
         <f>COUNTIF('student_exam_scores '!$L$2:$L$203,"pass")</f>
@@ -25581,7 +25194,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>169</v>
       </c>
@@ -25629,7 +25242,7 @@
         <v>Increase</v>
       </c>
       <c r="O15" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="P15">
         <v>34</v>
@@ -25639,7 +25252,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -25687,7 +25300,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -25735,10 +25348,10 @@
         <v>Increase</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>41</v>
       </c>
@@ -25786,14 +25399,14 @@
         <v>Increase</v>
       </c>
       <c r="O18" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="P18">
         <f>COUNTIF($M$2:$M$201,O18)</f>
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -25841,7 +25454,7 @@
         <v>Increase</v>
       </c>
       <c r="O19" s="15" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="P19">
         <f>COUNTIF($M$3:$M$201,O19)</f>
@@ -25849,7 +25462,7 @@
       </c>
       <c r="Q19" s="15"/>
     </row>
-    <row r="20" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -25897,7 +25510,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>188</v>
       </c>
@@ -25945,7 +25558,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -25993,7 +25606,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -26041,7 +25654,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -26089,7 +25702,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>106</v>
       </c>
@@ -26137,7 +25750,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -26185,7 +25798,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -26233,7 +25846,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>89</v>
       </c>
@@ -26281,7 +25894,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>9</v>
       </c>
@@ -26329,7 +25942,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -26377,7 +25990,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -26425,7 +26038,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -26473,7 +26086,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -26521,7 +26134,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -26569,7 +26182,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -26617,7 +26230,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -26665,7 +26278,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -26713,7 +26326,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -26761,7 +26374,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -26809,7 +26422,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -26857,7 +26470,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -26905,7 +26518,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -26953,7 +26566,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>159</v>
       </c>
@@ -27001,7 +26614,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -27049,7 +26662,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -27097,7 +26710,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>1</v>
       </c>
@@ -27145,7 +26758,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -27193,7 +26806,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>160</v>
       </c>
@@ -27241,7 +26854,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -27289,7 +26902,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>48</v>
       </c>
@@ -27337,7 +26950,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>49</v>
       </c>
@@ -27385,7 +26998,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -27433,7 +27046,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>44</v>
       </c>
@@ -27481,7 +27094,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>52</v>
       </c>
@@ -27529,7 +27142,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>53</v>
       </c>
@@ -27577,7 +27190,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="56" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -27625,7 +27238,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="57" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -27673,7 +27286,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>148</v>
       </c>
@@ -27721,7 +27334,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>57</v>
       </c>
@@ -27769,7 +27382,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>113</v>
       </c>
@@ -27817,7 +27430,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>59</v>
       </c>
@@ -27865,7 +27478,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>60</v>
       </c>
@@ -27913,7 +27526,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>61</v>
       </c>
@@ -27961,7 +27574,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>62</v>
       </c>
@@ -28009,7 +27622,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>63</v>
       </c>
@@ -28057,7 +27670,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>64</v>
       </c>
@@ -28105,7 +27718,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>65</v>
       </c>
@@ -28153,7 +27766,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>66</v>
       </c>
@@ -28201,7 +27814,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>85</v>
       </c>
@@ -28249,7 +27862,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>68</v>
       </c>
@@ -28297,7 +27910,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>69</v>
       </c>
@@ -28345,7 +27958,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>27</v>
       </c>
@@ -28393,7 +28006,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>71</v>
       </c>
@@ -28441,7 +28054,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>72</v>
       </c>
@@ -28489,7 +28102,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="75" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>73</v>
       </c>
@@ -28537,7 +28150,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>74</v>
       </c>
@@ -28585,7 +28198,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>75</v>
       </c>
@@ -28633,7 +28246,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>76</v>
       </c>
@@ -28681,7 +28294,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="79" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>77</v>
       </c>
@@ -28729,7 +28342,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="80" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>78</v>
       </c>
@@ -28777,7 +28390,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="81" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>79</v>
       </c>
@@ -28825,7 +28438,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="82" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>80</v>
       </c>
@@ -28873,7 +28486,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="83" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>81</v>
       </c>
@@ -28921,7 +28534,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="84" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>82</v>
       </c>
@@ -28969,7 +28582,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="85" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>83</v>
       </c>
@@ -29017,7 +28630,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="86" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>84</v>
       </c>
@@ -29065,7 +28678,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="87" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>126</v>
       </c>
@@ -29113,7 +28726,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>86</v>
       </c>
@@ -29161,7 +28774,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="89" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>87</v>
       </c>
@@ -29209,7 +28822,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="90" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>90</v>
       </c>
@@ -29257,7 +28870,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="91" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>94</v>
       </c>
@@ -29305,7 +28918,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="92" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>197</v>
       </c>
@@ -29353,7 +28966,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="93" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>91</v>
       </c>
@@ -29401,7 +29014,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="94" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>92</v>
       </c>
@@ -29449,7 +29062,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="95" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>93</v>
       </c>
@@ -29497,7 +29110,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="96" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>131</v>
       </c>
@@ -29545,7 +29158,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="97" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>95</v>
       </c>
@@ -29593,7 +29206,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="98" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>96</v>
       </c>
@@ -29641,7 +29254,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="99" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>97</v>
       </c>
@@ -29689,7 +29302,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="100" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>98</v>
       </c>
@@ -29737,7 +29350,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="101" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>99</v>
       </c>
@@ -29785,7 +29398,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="102" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>16</v>
       </c>
@@ -29833,7 +29446,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="103" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>101</v>
       </c>
@@ -29881,7 +29494,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="104" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>102</v>
       </c>
@@ -29929,7 +29542,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="105" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>103</v>
       </c>
@@ -29977,7 +29590,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="106" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>104</v>
       </c>
@@ -30025,7 +29638,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="107" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>105</v>
       </c>
@@ -30073,7 +29686,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="108" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>26</v>
       </c>
@@ -30121,7 +29734,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="109" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>107</v>
       </c>
@@ -30169,7 +29782,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="110" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>108</v>
       </c>
@@ -30217,7 +29830,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="111" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>109</v>
       </c>
@@ -30265,7 +29878,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="112" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>110</v>
       </c>
@@ -30313,7 +29926,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="113" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>111</v>
       </c>
@@ -30361,7 +29974,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="114" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>112</v>
       </c>
@@ -30409,7 +30022,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="115" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>136</v>
       </c>
@@ -30457,7 +30070,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="116" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>114</v>
       </c>
@@ -30505,7 +30118,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="117" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>115</v>
       </c>
@@ -30553,7 +30166,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="118" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>116</v>
       </c>
@@ -30601,7 +30214,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="119" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>117</v>
       </c>
@@ -30649,7 +30262,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="120" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>118</v>
       </c>
@@ -30697,7 +30310,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="121" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>10</v>
       </c>
@@ -30745,7 +30358,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="122" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>120</v>
       </c>
@@ -30793,7 +30406,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="123" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>121</v>
       </c>
@@ -30841,7 +30454,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="124" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>122</v>
       </c>
@@ -30889,7 +30502,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="125" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>123</v>
       </c>
@@ -30937,7 +30550,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="126" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>154</v>
       </c>
@@ -30985,7 +30598,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="127" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>125</v>
       </c>
@@ -31033,7 +30646,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="128" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>119</v>
       </c>
@@ -31081,7 +30694,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="129" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>127</v>
       </c>
@@ -31129,7 +30742,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="130" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>128</v>
       </c>
@@ -31177,7 +30790,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="131" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>129</v>
       </c>
@@ -31225,7 +30838,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="132" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>130</v>
       </c>
@@ -31273,7 +30886,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="133" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>139</v>
       </c>
@@ -31321,7 +30934,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="134" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>132</v>
       </c>
@@ -31369,7 +30982,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="135" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>133</v>
       </c>
@@ -31417,7 +31030,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="136" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>165</v>
       </c>
@@ -31465,7 +31078,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="137" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>135</v>
       </c>
@@ -31513,7 +31126,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="138" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>13</v>
       </c>
@@ -31561,7 +31174,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="139" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>137</v>
       </c>
@@ -31609,7 +31222,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="140" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>138</v>
       </c>
@@ -31657,7 +31270,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="141" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>134</v>
       </c>
@@ -31705,7 +31318,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="142" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>140</v>
       </c>
@@ -31753,7 +31366,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="143" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>141</v>
       </c>
@@ -31801,7 +31414,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="144" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>142</v>
       </c>
@@ -31849,7 +31462,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="145" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>143</v>
       </c>
@@ -31897,7 +31510,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="146" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>144</v>
       </c>
@@ -31945,7 +31558,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="147" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>51</v>
       </c>
@@ -31993,7 +31606,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="148" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>146</v>
       </c>
@@ -32041,7 +31654,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="149" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>147</v>
       </c>
@@ -32089,7 +31702,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="150" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>176</v>
       </c>
@@ -32137,7 +31750,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="151" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>149</v>
       </c>
@@ -32185,7 +31798,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="152" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>150</v>
       </c>
@@ -32233,7 +31846,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="153" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>151</v>
       </c>
@@ -32281,7 +31894,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="154" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>152</v>
       </c>
@@ -32329,7 +31942,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="155" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>153</v>
       </c>
@@ -32377,7 +31990,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="156" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>12</v>
       </c>
@@ -32425,7 +32038,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="157" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>155</v>
       </c>
@@ -32473,7 +32086,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="158" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>156</v>
       </c>
@@ -32521,7 +32134,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="159" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>157</v>
       </c>
@@ -32569,7 +32182,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="160" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>158</v>
       </c>
@@ -32617,7 +32230,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="161" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>100</v>
       </c>
@@ -32665,7 +32278,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="162" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>46</v>
       </c>
@@ -32713,7 +32326,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="163" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>161</v>
       </c>
@@ -32761,7 +32374,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="164" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>162</v>
       </c>
@@ -32809,7 +32422,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="165" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>163</v>
       </c>
@@ -32857,7 +32470,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="166" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>164</v>
       </c>
@@ -32905,7 +32518,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="167" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>168</v>
       </c>
@@ -32953,7 +32566,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="168" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>166</v>
       </c>
@@ -33001,7 +32614,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="169" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>167</v>
       </c>
@@ -33049,7 +32662,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="170" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>88</v>
       </c>
@@ -33097,7 +32710,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="171" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>67</v>
       </c>
@@ -33145,7 +32758,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="172" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>170</v>
       </c>
@@ -33193,7 +32806,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="173" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>171</v>
       </c>
@@ -33244,7 +32857,7 @@
       <c r="P173" s="18"/>
       <c r="Q173" s="18"/>
     </row>
-    <row r="174" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>172</v>
       </c>
@@ -33295,7 +32908,7 @@
       <c r="P174" s="15"/>
       <c r="Q174" s="15"/>
     </row>
-    <row r="175" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>173</v>
       </c>
@@ -33346,7 +32959,7 @@
       <c r="P175" s="15"/>
       <c r="Q175" s="15"/>
     </row>
-    <row r="176" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>174</v>
       </c>
@@ -33397,7 +33010,7 @@
       <c r="P176" s="15"/>
       <c r="Q176" s="15"/>
     </row>
-    <row r="177" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>145</v>
       </c>
@@ -33448,7 +33061,7 @@
       <c r="P177" s="15"/>
       <c r="Q177" s="15"/>
     </row>
-    <row r="178" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>58</v>
       </c>
@@ -33499,7 +33112,7 @@
       <c r="P178" s="15"/>
       <c r="Q178" s="15"/>
     </row>
-    <row r="179" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>177</v>
       </c>
@@ -33550,7 +33163,7 @@
       <c r="P179" s="15"/>
       <c r="Q179" s="15"/>
     </row>
-    <row r="180" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>178</v>
       </c>
@@ -33601,7 +33214,7 @@
       <c r="P180" s="15"/>
       <c r="Q180" s="15"/>
     </row>
-    <row r="181" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>179</v>
       </c>
@@ -33652,7 +33265,7 @@
       <c r="P181" s="21"/>
       <c r="Q181" s="15"/>
     </row>
-    <row r="182" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>180</v>
       </c>
@@ -33703,7 +33316,7 @@
       <c r="P182" s="15"/>
       <c r="Q182" s="15"/>
     </row>
-    <row r="183" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>181</v>
       </c>
@@ -33751,7 +33364,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="184" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>182</v>
       </c>
@@ -33800,7 +33413,7 @@
       </c>
       <c r="O184" s="1"/>
     </row>
-    <row r="185" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>175</v>
       </c>
@@ -33848,7 +33461,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="186" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>184</v>
       </c>
@@ -33898,7 +33511,7 @@
       <c r="O186" s="15"/>
       <c r="Q186" s="15"/>
     </row>
-    <row r="187" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>185</v>
       </c>
@@ -33946,7 +33559,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="188" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>186</v>
       </c>
@@ -33994,7 +33607,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="189" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>187</v>
       </c>
@@ -34042,7 +33655,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="190" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>56</v>
       </c>
@@ -34090,7 +33703,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="191" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>189</v>
       </c>
@@ -34138,7 +33751,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="192" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>190</v>
       </c>
@@ -34186,7 +33799,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="193" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>191</v>
       </c>
@@ -34234,7 +33847,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="194" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>192</v>
       </c>
@@ -34282,7 +33895,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="195" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>193</v>
       </c>
@@ -34330,7 +33943,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="196" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>194</v>
       </c>
@@ -34378,7 +33991,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="197" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>195</v>
       </c>
@@ -34426,7 +34039,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="198" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>196</v>
       </c>
@@ -34474,7 +34087,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="199" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>23</v>
       </c>
@@ -34522,7 +34135,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="200" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>198</v>
       </c>
@@ -34570,7 +34183,7 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="201" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>199</v>
       </c>
@@ -34618,13 +34231,13 @@
         <v>Increase</v>
       </c>
     </row>
-    <row r="202" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C202" s="4"/>
       <c r="E202" s="4"/>
       <c r="G202" s="4"/>
       <c r="H202" s="4"/>
     </row>
-    <row r="203" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C203" s="4"/>
       <c r="G203" s="4"/>
       <c r="H203" s="4"/>
@@ -34649,16 +34262,15 @@
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="15.5546875" customWidth="1"/>
     <col min="3" max="3" width="5" customWidth="1"/>
-    <col min="4" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="10.77734375" customWidth="1"/>
+    <col min="4" max="6" width="6" customWidth="1"/>
+    <col min="7" max="8" width="10.77734375" customWidth="1"/>
     <col min="9" max="9" width="5.109375" customWidth="1"/>
     <col min="10" max="11" width="4.5546875" customWidth="1"/>
     <col min="12" max="12" width="21.44140625" customWidth="1"/>
     <col min="13" max="13" width="15.5546875" customWidth="1"/>
     <col min="14" max="16" width="3.6640625" customWidth="1"/>
     <col min="17" max="17" width="4.6640625" customWidth="1"/>
-    <col min="18" max="18" width="5.6640625" customWidth="1"/>
-    <col min="19" max="19" width="10.77734375" customWidth="1"/>
+    <col min="18" max="19" width="10.77734375" customWidth="1"/>
     <col min="20" max="22" width="4.5546875" customWidth="1"/>
     <col min="23" max="23" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="5.6640625" bestFit="1" customWidth="1"/>
@@ -34688,7 +34300,7 @@
   <sheetData>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="L2" s="5" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="M2" s="5" t="s">
         <v>207</v>
@@ -34698,7 +34310,6 @@
       <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
       <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
@@ -34712,7 +34323,6 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
       <c r="L3" s="5" t="s">
         <v>205</v>
       </c>
@@ -34732,9 +34342,6 @@
         <v>212</v>
       </c>
       <c r="R3" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="S3" s="7" t="s">
         <v>206</v>
       </c>
     </row>
@@ -34758,9 +34365,6 @@
         <v>212</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="H4" s="7" t="s">
         <v>206</v>
       </c>
       <c r="L4" s="9" t="s">
@@ -34782,10 +34386,7 @@
         <v>6</v>
       </c>
       <c r="R4" s="8">
-        <v>4</v>
-      </c>
-      <c r="S4" s="8">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="U4" s="4"/>
     </row>
@@ -34794,10 +34395,10 @@
         <v>234</v>
       </c>
       <c r="B5" s="8">
-        <v>20.799999999999997</v>
+        <v>20.8</v>
       </c>
       <c r="C5" s="8">
-        <v>36.800000000000004</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="D5" s="8">
         <v>68.599999999999994</v>
@@ -34809,136 +34410,118 @@
         <v>58.699999999999996</v>
       </c>
       <c r="G5" s="8">
-        <v>45.400000000000006</v>
-      </c>
-      <c r="H5" s="8">
-        <v>293.79999999999995</v>
+        <v>248.39999999999998</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="M5" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N5" s="8">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O5" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P5" s="8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q5" s="8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R5" s="8">
-        <v>5</v>
-      </c>
-      <c r="S5" s="8">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="U5" s="4"/>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="B6" s="8">
+        <v>11.700000000000001</v>
+      </c>
+      <c r="C6" s="8">
+        <v>41.5</v>
+      </c>
+      <c r="D6" s="8">
+        <v>37</v>
+      </c>
+      <c r="E6" s="8">
+        <v>55.2</v>
+      </c>
+      <c r="F6" s="8">
+        <v>72.100000000000009</v>
+      </c>
+      <c r="G6" s="8">
+        <v>217.5</v>
+      </c>
+      <c r="L6" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="B6" s="8">
-        <v>8.1000000000000014</v>
-      </c>
-      <c r="C6" s="8">
-        <v>45.400000000000006</v>
-      </c>
-      <c r="D6" s="8">
-        <v>23.700000000000003</v>
-      </c>
-      <c r="E6" s="8">
-        <v>70.600000000000009</v>
-      </c>
-      <c r="F6" s="8">
-        <v>48.6</v>
-      </c>
-      <c r="G6" s="8">
-        <v>57.199999999999996</v>
-      </c>
-      <c r="H6" s="8">
-        <v>253.6</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>214</v>
-      </c>
       <c r="M6" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N6" s="8">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O6" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P6" s="8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q6" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R6" s="8">
-        <v>3</v>
-      </c>
-      <c r="S6" s="8">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="U6" s="4"/>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="B7" s="8">
-        <v>11.700000000000001</v>
+        <v>8.1000000000000014</v>
       </c>
       <c r="C7" s="8">
-        <v>41.5</v>
+        <v>45.400000000000006</v>
       </c>
       <c r="D7" s="8">
-        <v>37</v>
+        <v>23.7</v>
       </c>
       <c r="E7" s="8">
-        <v>55.2</v>
+        <v>70.600000000000009</v>
       </c>
       <c r="F7" s="8">
-        <v>72.100000000000009</v>
+        <v>48.6</v>
       </c>
       <c r="G7" s="8">
-        <v>35.1</v>
-      </c>
-      <c r="H7" s="8">
-        <v>252.6</v>
+        <v>196.4</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M7" s="8">
         <v>6</v>
       </c>
       <c r="N7" s="8">
+        <v>6</v>
+      </c>
+      <c r="O7" s="8">
         <v>7</v>
       </c>
-      <c r="O7" s="8">
+      <c r="P7" s="8">
         <v>6</v>
       </c>
-      <c r="P7" s="8">
-        <v>4</v>
-      </c>
       <c r="Q7" s="8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R7" s="8">
-        <v>5</v>
-      </c>
-      <c r="S7" s="8">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="U7" s="4"/>
     </row>
@@ -34962,34 +34545,28 @@
         <v>90.2</v>
       </c>
       <c r="G8" s="8">
-        <v>57.7</v>
-      </c>
-      <c r="H8" s="8">
-        <v>251.10000000000002</v>
+        <v>193.4</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="M8" s="8">
         <v>6</v>
       </c>
       <c r="N8" s="8">
+        <v>7</v>
+      </c>
+      <c r="O8" s="8">
         <v>6</v>
       </c>
-      <c r="O8" s="8">
-        <v>7</v>
-      </c>
       <c r="P8" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q8" s="8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R8" s="8">
-        <v>2</v>
-      </c>
-      <c r="S8" s="8">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="U8" s="4"/>
     </row>
@@ -35013,10 +34590,7 @@
         <v>70.7</v>
       </c>
       <c r="G9" s="8">
-        <v>23.5</v>
-      </c>
-      <c r="H9" s="8">
-        <v>214</v>
+        <v>190.5</v>
       </c>
       <c r="L9" s="9" t="s">
         <v>206</v>
@@ -35037,10 +34611,7 @@
         <v>34</v>
       </c>
       <c r="R9" s="8">
-        <v>19</v>
-      </c>
-      <c r="S9" s="8">
-        <v>200</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.3">
@@ -35054,7 +34625,7 @@
         <v>171</v>
       </c>
       <c r="D10" s="8">
-        <v>203.60000000000002</v>
+        <v>203.6</v>
       </c>
       <c r="E10" s="8">
         <v>267.40000000000003</v>
@@ -35063,10 +34634,7 @@
         <v>340.30000000000007</v>
       </c>
       <c r="G10" s="8">
-        <v>218.9</v>
-      </c>
-      <c r="H10" s="8">
-        <v>1265.0999999999999</v>
+        <v>1046.1999999999998</v>
       </c>
     </row>
   </sheetData>
@@ -35084,7 +34652,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A4:C11"/>
+  <dimension ref="A4:C10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.77734375" customWidth="1"/>
@@ -35117,79 +34685,68 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>236</v>
+        <v>212</v>
       </c>
       <c r="B5" s="8">
-        <v>66.315789473684205</v>
+        <v>70.352941176470594</v>
       </c>
       <c r="C5" s="8">
-        <v>43.136842105263156</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B6" s="8">
-        <v>70.352941176470594</v>
+        <v>67.17647058823529</v>
       </c>
       <c r="C6" s="8">
-        <v>40.1</v>
+        <v>35.761764705882349</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B7" s="8">
-        <v>67.17647058823529</v>
+        <v>66.147058823529406</v>
       </c>
       <c r="C7" s="8">
-        <v>35.761764705882349</v>
+        <v>33.529411764705884</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B8" s="8">
-        <v>66.147058823529406</v>
+        <v>63.422222222222224</v>
       </c>
       <c r="C8" s="8">
-        <v>33.529411764705884</v>
+        <v>29.211111111111105</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B9" s="8">
-        <v>63.422222222222224</v>
+        <v>68.264705882352942</v>
       </c>
       <c r="C9" s="8">
-        <v>29.211111111111116</v>
+        <v>27.576470588235303</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B10" s="8">
-        <v>68.264705882352942</v>
+        <v>66.850828729281773</v>
       </c>
       <c r="C10" s="8">
-        <v>27.576470588235303</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="B11" s="8">
-        <v>66.8</v>
-      </c>
-      <c r="C11" s="8">
-        <v>33.954999999999991</v>
+        <v>32.991160220994473</v>
       </c>
     </row>
   </sheetData>
@@ -35210,9 +34767,9 @@
   <dimension ref="A3:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.109375" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -35273,6 +34830,13 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId3"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -35299,7 +34863,7 @@
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B3" s="22" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C3">
         <f>COUNTIF('student_exam_scores '!$I$2:$I$201,B3)</f>
@@ -35311,7 +34875,7 @@
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B4" s="22" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C4">
         <f>COUNTIF('student_exam_scores '!$I$2:$I$201,B4)</f>
@@ -35323,7 +34887,7 @@
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B5" s="22" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C5">
         <f>COUNTIF('student_exam_scores '!$I$2:$I$201,B5)</f>
@@ -35335,7 +34899,7 @@
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B6" s="22" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C6">
         <f>COUNTIF('student_exam_scores '!$I$2:$I$201,B6)</f>
@@ -35347,7 +34911,7 @@
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B7" s="22" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C7">
         <f>COUNTIF('student_exam_scores '!$I$2:$I$201,B7)</f>
@@ -35359,18 +34923,18 @@
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B9" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="D9" s="22" t="s">
         <v>238</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>239</v>
-      </c>
-      <c r="D9" s="22" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B10" s="22" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C10">
         <v>34</v>
@@ -35382,7 +34946,7 @@
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B11" s="22" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C11">
         <f>COUNTIF('student_exam_scores '!$L$2:$L$203,"pass")</f>
@@ -35395,12 +34959,12 @@
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B13" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B14" s="22" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C14">
         <f>COUNTIF('student_exam_scores '!$M$2:$M$201,B14)</f>
@@ -35409,7 +34973,7 @@
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B15" s="22" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C15">
         <f>COUNTIF('student_exam_scores '!$M$2:$M$201,B15)</f>
@@ -35504,7 +35068,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:B10"/>
+  <dimension ref="A3:B9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" customWidth="1"/>
@@ -35555,34 +35119,26 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
       <c r="B7" s="8">
-        <v>66.315789473684205</v>
+        <v>66.147058823529406</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B8" s="8">
-        <v>66.147058823529406</v>
+        <v>63.422222222222224</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B9" s="8">
-        <v>63.422222222222224</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="B10" s="8">
-        <v>66.8</v>
+        <v>66.850828729281773</v>
       </c>
     </row>
   </sheetData>
@@ -35593,7 +35149,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:B10"/>
+  <dimension ref="A3:B9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" customWidth="1"/>
@@ -35620,58 +35176,50 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="B4" s="8">
-        <v>43.136842105263156</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B5" s="8">
-        <v>40.1</v>
+        <v>35.761764705882349</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B6" s="8">
-        <v>35.761764705882349</v>
+        <v>33.529411764705884</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B7" s="8">
-        <v>33.529411764705884</v>
+        <v>29.211111111111105</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B8" s="8">
-        <v>29.211111111111116</v>
+        <v>27.576470588235303</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="B9" s="8">
-        <v>27.576470588235303</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="B10" s="8">
-        <v>33.954999999999991</v>
+        <v>32.991160220994473</v>
       </c>
     </row>
   </sheetData>
